--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119669941</v>
+        <v>119669869</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>97882</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,34 +1512,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219797</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566558</v>
+        <v>566532</v>
       </c>
       <c r="R9" t="n">
-        <v>6411939</v>
+        <v>6411863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119669869</v>
+        <v>119669941</v>
       </c>
       <c r="B10" t="n">
-        <v>97882</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,42 +1631,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219797</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566532</v>
+        <v>566558</v>
       </c>
       <c r="R10" t="n">
-        <v>6411863</v>
+        <v>6411939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1049,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119669893</v>
+        <v>119670067</v>
       </c>
       <c r="B5" t="n">
-        <v>109824</v>
+        <v>105009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,25 +1065,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1093,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566535</v>
+        <v>566514</v>
       </c>
       <c r="R5" t="n">
-        <v>6411902</v>
+        <v>6411864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119670147</v>
+        <v>119669941</v>
       </c>
       <c r="B6" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,42 +1172,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1212,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566479</v>
+        <v>566558</v>
       </c>
       <c r="R6" t="n">
-        <v>6411867</v>
+        <v>6411939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119670085</v>
+        <v>119670236</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,35 +1283,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566545</v>
+        <v>566532</v>
       </c>
       <c r="R7" t="n">
-        <v>6411969</v>
+        <v>6411909</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1367,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119670236</v>
+        <v>119670112</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1397,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1424,13 +1423,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1438,13 +1432,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566532</v>
+        <v>566522</v>
       </c>
       <c r="R8" t="n">
-        <v>6411909</v>
+        <v>6411938</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,6 +1476,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1500,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119669869</v>
+        <v>119670004</v>
       </c>
       <c r="B9" t="n">
-        <v>97882</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,21 +1511,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219797</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1540,15 +1535,10 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1556,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566532</v>
+        <v>566519</v>
       </c>
       <c r="R9" t="n">
-        <v>6411863</v>
+        <v>6411943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,7 +1609,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119669941</v>
+        <v>119670030</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1667,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566558</v>
+        <v>566559</v>
       </c>
       <c r="R10" t="n">
-        <v>6411939</v>
+        <v>6411929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,7 +1720,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119669924</v>
+        <v>119669969</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1778,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566520</v>
+        <v>566532</v>
       </c>
       <c r="R11" t="n">
-        <v>6411922</v>
+        <v>6411952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119670097</v>
+        <v>119669893</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>109824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,33 +1843,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1889,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566515</v>
+        <v>566535</v>
       </c>
       <c r="R12" t="n">
-        <v>6411951</v>
+        <v>6411902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119670004</v>
+        <v>119669869</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>97882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>219797</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1992,10 +1978,15 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2003,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566519</v>
+        <v>566532</v>
       </c>
       <c r="R13" t="n">
-        <v>6411943</v>
+        <v>6411863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119670112</v>
+        <v>119670147</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>105009</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,30 +2073,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566522</v>
+        <v>566479</v>
       </c>
       <c r="R14" t="n">
-        <v>6411938</v>
+        <v>6411867</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119669969</v>
+        <v>119670097</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566532</v>
+        <v>566515</v>
       </c>
       <c r="R15" t="n">
-        <v>6411952</v>
+        <v>6411951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670067</v>
+        <v>119670085</v>
       </c>
       <c r="B16" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,25 +2299,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566514</v>
+        <v>566545</v>
       </c>
       <c r="R16" t="n">
-        <v>6411864</v>
+        <v>6411969</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119670030</v>
+        <v>119669924</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566559</v>
+        <v>566520</v>
       </c>
       <c r="R17" t="n">
-        <v>6411929</v>
+        <v>6411922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119689486</v>
+        <v>119689566</v>
       </c>
       <c r="B18" t="n">
-        <v>57461</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,39 +2521,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2561,13 +2557,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566551</v>
+        <v>566514</v>
       </c>
       <c r="R18" t="n">
-        <v>6411949</v>
+        <v>6411943</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,6 +2601,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2623,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119689566</v>
+        <v>119689486</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>57461</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,35 +2632,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2671,13 +2672,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566514</v>
+        <v>566551</v>
       </c>
       <c r="R19" t="n">
-        <v>6411943</v>
+        <v>6411949</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,7 +2716,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1049,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119670067</v>
+        <v>119669869</v>
       </c>
       <c r="B5" t="n">
-        <v>105009</v>
+        <v>97882</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,30 +1065,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1097,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566514</v>
+        <v>566532</v>
       </c>
       <c r="R5" t="n">
-        <v>6411864</v>
+        <v>6411863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119669941</v>
+        <v>119670112</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,35 +1180,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566558</v>
+        <v>566522</v>
       </c>
       <c r="R6" t="n">
-        <v>6411939</v>
+        <v>6411938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119670236</v>
+        <v>119670085</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,39 +1290,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566532</v>
+        <v>566545</v>
       </c>
       <c r="R7" t="n">
-        <v>6411909</v>
+        <v>6411969</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,6 +1370,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119670112</v>
+        <v>119670004</v>
       </c>
       <c r="B8" t="n">
         <v>91840</v>
@@ -1420,10 +1424,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1432,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566522</v>
+        <v>566519</v>
       </c>
       <c r="R8" t="n">
-        <v>6411938</v>
+        <v>6411943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119670004</v>
+        <v>119669924</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,38 +1515,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566519</v>
+        <v>566520</v>
       </c>
       <c r="R9" t="n">
-        <v>6411943</v>
+        <v>6411922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119670030</v>
+        <v>119670147</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,34 +1626,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1657,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566559</v>
+        <v>566479</v>
       </c>
       <c r="R10" t="n">
-        <v>6411929</v>
+        <v>6411867</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119669969</v>
+        <v>119669893</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>109824</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,33 +1745,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1768,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566532</v>
+        <v>566535</v>
       </c>
       <c r="R11" t="n">
-        <v>6411952</v>
+        <v>6411902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119669893</v>
+        <v>119670236</v>
       </c>
       <c r="B12" t="n">
-        <v>109824</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,31 +1852,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1875,13 +1892,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566535</v>
+        <v>566532</v>
       </c>
       <c r="R12" t="n">
-        <v>6411902</v>
+        <v>6411909</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,7 +1936,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119669869</v>
+        <v>119670030</v>
       </c>
       <c r="B13" t="n">
-        <v>97882</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,42 +1966,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219797</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1994,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566532</v>
+        <v>566559</v>
       </c>
       <c r="R13" t="n">
-        <v>6411863</v>
+        <v>6411929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +2065,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119670147</v>
+        <v>119670067</v>
       </c>
       <c r="B14" t="n">
         <v>105009</v>
@@ -2090,21 +2098,13 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566479</v>
+        <v>566514</v>
       </c>
       <c r="R14" t="n">
-        <v>6411867</v>
+        <v>6411864</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670097</v>
+        <v>119669941</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566515</v>
+        <v>566558</v>
       </c>
       <c r="R15" t="n">
-        <v>6411951</v>
+        <v>6411939</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670085</v>
+        <v>119670097</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566545</v>
+        <v>566515</v>
       </c>
       <c r="R16" t="n">
-        <v>6411969</v>
+        <v>6411951</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119669924</v>
+        <v>119669969</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566520</v>
+        <v>566532</v>
       </c>
       <c r="R17" t="n">
-        <v>6411922</v>
+        <v>6411952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119689566</v>
+        <v>119689486</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>57461</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,35 +2521,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2557,13 +2561,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566514</v>
+        <v>566551</v>
       </c>
       <c r="R18" t="n">
-        <v>6411943</v>
+        <v>6411949</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2605,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2620,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119689486</v>
+        <v>119689566</v>
       </c>
       <c r="B19" t="n">
-        <v>57461</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,39 +2635,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2672,13 +2671,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566551</v>
+        <v>566514</v>
       </c>
       <c r="R19" t="n">
-        <v>6411949</v>
+        <v>6411943</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2716,6 +2715,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119670067</v>
+        <v>119669941</v>
       </c>
       <c r="B14" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,25 +2077,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566514</v>
+        <v>566558</v>
       </c>
       <c r="R14" t="n">
-        <v>6411864</v>
+        <v>6411939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119669941</v>
+        <v>119670097</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566558</v>
+        <v>566515</v>
       </c>
       <c r="R15" t="n">
-        <v>6411939</v>
+        <v>6411951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670097</v>
+        <v>119670067</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,25 +2299,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566515</v>
+        <v>566514</v>
       </c>
       <c r="R16" t="n">
-        <v>6411951</v>
+        <v>6411864</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1049,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119669869</v>
+        <v>119670236</v>
       </c>
       <c r="B5" t="n">
-        <v>97882</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,43 +1061,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1108,10 +1104,10 @@
         <v>566532</v>
       </c>
       <c r="R5" t="n">
-        <v>6411863</v>
+        <v>6411909</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1149,7 +1145,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119670112</v>
+        <v>119669869</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>97882</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,30 +1179,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566522</v>
+        <v>566532</v>
       </c>
       <c r="R6" t="n">
-        <v>6411938</v>
+        <v>6411863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1389,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119670004</v>
+        <v>119670112</v>
       </c>
       <c r="B8" t="n">
         <v>91840</v>
@@ -1424,14 +1428,10 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566519</v>
+        <v>566522</v>
       </c>
       <c r="R8" t="n">
-        <v>6411943</v>
+        <v>6411938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119669924</v>
+        <v>119669969</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566520</v>
+        <v>566532</v>
       </c>
       <c r="R9" t="n">
-        <v>6411922</v>
+        <v>6411952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119670147</v>
+        <v>119669893</v>
       </c>
       <c r="B10" t="n">
-        <v>105009</v>
+        <v>109824</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,38 +1630,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219677</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1670,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566479</v>
+        <v>566535</v>
       </c>
       <c r="R10" t="n">
-        <v>6411867</v>
+        <v>6411902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119669893</v>
+        <v>119670030</v>
       </c>
       <c r="B11" t="n">
-        <v>109824</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,29 +1733,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1777,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566535</v>
+        <v>566559</v>
       </c>
       <c r="R11" t="n">
-        <v>6411902</v>
+        <v>6411929</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119670236</v>
+        <v>119669941</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,39 +1844,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1892,13 +1880,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566532</v>
+        <v>566558</v>
       </c>
       <c r="R12" t="n">
-        <v>6411909</v>
+        <v>6411939</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,6 +1924,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1954,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119670030</v>
+        <v>119670067</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,25 +1955,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566559</v>
+        <v>566514</v>
       </c>
       <c r="R13" t="n">
-        <v>6411929</v>
+        <v>6411864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2054,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119669941</v>
+        <v>119669924</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2113,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566558</v>
+        <v>566520</v>
       </c>
       <c r="R14" t="n">
-        <v>6411939</v>
+        <v>6411922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670067</v>
+        <v>119670004</v>
       </c>
       <c r="B16" t="n">
-        <v>105009</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,31 +2292,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2335,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566514</v>
+        <v>566519</v>
       </c>
       <c r="R16" t="n">
-        <v>6411864</v>
+        <v>6411943</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119669969</v>
+        <v>119670147</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,34 +2402,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566532</v>
+        <v>566479</v>
       </c>
       <c r="R17" t="n">
-        <v>6411952</v>
+        <v>6411867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119689486</v>
+        <v>119689566</v>
       </c>
       <c r="B18" t="n">
-        <v>57461</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,39 +2521,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2561,13 +2557,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566551</v>
+        <v>566514</v>
       </c>
       <c r="R18" t="n">
-        <v>6411949</v>
+        <v>6411943</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,6 +2601,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2623,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119689566</v>
+        <v>119689486</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>57461</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,35 +2632,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2671,13 +2672,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566514</v>
+        <v>566551</v>
       </c>
       <c r="R19" t="n">
-        <v>6411943</v>
+        <v>6411949</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,7 +2716,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119669941</v>
+        <v>119670067</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566558</v>
+        <v>566514</v>
       </c>
       <c r="R12" t="n">
-        <v>6411939</v>
+        <v>6411864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119670067</v>
+        <v>119669941</v>
       </c>
       <c r="B13" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,25 +1955,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566514</v>
+        <v>566558</v>
       </c>
       <c r="R13" t="n">
-        <v>6411864</v>
+        <v>6411939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670097</v>
+        <v>119670004</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,35 +2177,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2213,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566515</v>
+        <v>566519</v>
       </c>
       <c r="R15" t="n">
-        <v>6411951</v>
+        <v>6411943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670004</v>
+        <v>119670097</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,38 +2291,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566519</v>
+        <v>566515</v>
       </c>
       <c r="R16" t="n">
-        <v>6411943</v>
+        <v>6411951</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119669893</v>
+        <v>119670030</v>
       </c>
       <c r="B10" t="n">
-        <v>109824</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,29 +1626,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1658,10 +1662,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566535</v>
+        <v>566559</v>
       </c>
       <c r="R10" t="n">
-        <v>6411902</v>
+        <v>6411929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119670030</v>
+        <v>119669893</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>109824</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,33 +1737,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566559</v>
+        <v>566535</v>
       </c>
       <c r="R11" t="n">
-        <v>6411929</v>
+        <v>6411902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119670067</v>
+        <v>119669941</v>
       </c>
       <c r="B12" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566514</v>
+        <v>566558</v>
       </c>
       <c r="R12" t="n">
-        <v>6411864</v>
+        <v>6411939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119669941</v>
+        <v>119670067</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,25 +1955,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566558</v>
+        <v>566514</v>
       </c>
       <c r="R13" t="n">
-        <v>6411939</v>
+        <v>6411864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670004</v>
+        <v>119670097</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,38 +2177,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2216,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566519</v>
+        <v>566515</v>
       </c>
       <c r="R15" t="n">
-        <v>6411943</v>
+        <v>6411951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670097</v>
+        <v>119670004</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,35 +2288,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566515</v>
+        <v>566519</v>
       </c>
       <c r="R16" t="n">
-        <v>6411951</v>
+        <v>6411943</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566442.2075239469</v>
+        <v>566442</v>
       </c>
       <c r="R2" t="n">
-        <v>6411922.74334718</v>
+        <v>6411923</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1968-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1968-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110493</v>
+        <v>110502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110507</v>
+        <v>110535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110535</v>
+        <v>110541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110541</v>
+        <v>110548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110548</v>
+        <v>110552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110552</v>
+        <v>110560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110563</v>
+        <v>110568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110568</v>
+        <v>110576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465340</v>
       </c>
       <c r="B2" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">

--- a/artfynd/A 35134-2024 artfynd.xlsx
+++ b/artfynd/A 35134-2024 artfynd.xlsx
@@ -675,48 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74465340</v>
+        <v>95953188</v>
       </c>
       <c r="B2" t="n">
-        <v>110586</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högsby 500 m SV, Sm</t>
+          <t>A44454, Skutterstad, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566442</v>
+        <v>566491</v>
       </c>
       <c r="R2" t="n">
-        <v>6411923</v>
+        <v>6411865</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,88 +751,80 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1968-01-01</t>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1968-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G2d 3336. SOM: Hedera helix. LEG: Gunvald Bruce. KOM: även 1930-talet Det.</t>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsbryn, igenväxande</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95953007</v>
+        <v>119670004</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A44454, Skutterstad, Sm</t>
+          <t>A 35134,  Hallången, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566469.97155105</v>
+        <v>566519</v>
       </c>
       <c r="R3" t="n">
-        <v>6411921.07315533</v>
+        <v>6411943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,22 +896,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95953188</v>
+        <v>119670112</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,45 +914,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A44454, Skutterstad, Sm</t>
+          <t>A 35134,  Hallången, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566490.6354640929</v>
+        <v>566522</v>
       </c>
       <c r="R4" t="n">
-        <v>6411864.982863821</v>
+        <v>6411938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,29 +975,19 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -1027,44 +1001,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119670236</v>
+        <v>95953007</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,27 +1041,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 35134,  Hallången, Sm</t>
+          <t>A44454, Skutterstad, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566532</v>
+        <v>566470</v>
       </c>
       <c r="R5" t="n">
-        <v>6411909</v>
+        <v>6411921</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,12 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1108,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,22 +1120,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119669869</v>
+        <v>119670236</v>
       </c>
       <c r="B6" t="n">
-        <v>97882</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,39 +1138,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1177,10 @@
         <v>566532</v>
       </c>
       <c r="R6" t="n">
-        <v>6411863</v>
+        <v>6411909</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,47 +1236,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119670085</v>
+        <v>119689486</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566545</v>
+        <v>566551</v>
       </c>
       <c r="R7" t="n">
-        <v>6411969</v>
+        <v>6411949</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1378,15 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119670112</v>
+        <v>74465340</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,44 +1356,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>219677</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 35134,  Hallången, Sm</t>
+          <t>Högsby 500 m SV, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566522</v>
+        <v>566442</v>
       </c>
       <c r="R8" t="n">
-        <v>6411938</v>
+        <v>6411923</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,12 +1410,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>1968-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>1968-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G2d 3336. SOM: Hedera helix. LEG: Gunvald Bruce. KOM: även 1930-talet Det.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,64 +1429,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsbryn, igenväxande</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119669969</v>
+        <v>119669893</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1536,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566532</v>
+        <v>566535</v>
       </c>
       <c r="R9" t="n">
-        <v>6411952</v>
+        <v>6411902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,46 +1558,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119670030</v>
+        <v>119669869</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1647,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566559</v>
+        <v>566532</v>
       </c>
       <c r="R10" t="n">
-        <v>6411929</v>
+        <v>6411863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,41 +1672,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119669893</v>
+        <v>119669924</v>
       </c>
       <c r="B11" t="n">
-        <v>109824</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1754,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566535</v>
+        <v>566520</v>
       </c>
       <c r="R11" t="n">
-        <v>6411902</v>
+        <v>6411922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,12 +1781,7 @@
         <v>119669941</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,37 +1884,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119670067</v>
+        <v>119669969</v>
       </c>
       <c r="B13" t="n">
-        <v>105009</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1976,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566514</v>
+        <v>566532</v>
       </c>
       <c r="R13" t="n">
-        <v>6411864</v>
+        <v>6411952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,15 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119669924</v>
+        <v>119670030</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566520</v>
+        <v>566559</v>
       </c>
       <c r="R14" t="n">
-        <v>6411922</v>
+        <v>6411929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,15 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670097</v>
+        <v>119670085</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566515</v>
+        <v>566545</v>
       </c>
       <c r="R15" t="n">
-        <v>6411951</v>
+        <v>6411969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,50 +2202,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670004</v>
+        <v>119670097</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2312,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566519</v>
+        <v>566515</v>
       </c>
       <c r="R16" t="n">
-        <v>6411943</v>
+        <v>6411951</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,54 +2308,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119670147</v>
+        <v>119689566</v>
       </c>
       <c r="B17" t="n">
-        <v>105009</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2431,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566479</v>
+        <v>566514</v>
       </c>
       <c r="R17" t="n">
-        <v>6411867</v>
+        <v>6411943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,37 +2414,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119689566</v>
+        <v>119670067</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2545,7 +2460,7 @@
         <v>566514</v>
       </c>
       <c r="R18" t="n">
-        <v>6411943</v>
+        <v>6411864</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,51 +2520,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119689486</v>
+        <v>119670147</v>
       </c>
       <c r="B19" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2657,13 +2571,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566551</v>
+        <v>566479</v>
       </c>
       <c r="R19" t="n">
-        <v>6411949</v>
+        <v>6411867</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,6 +2615,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
